--- a/kobo/gestores_semana5_diagnostico.xlsx
+++ b/kobo/gestores_semana5_diagnostico.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nome da escola</t>
+          <t>Nome do local de atuação</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Código INEP (8 dígitos; deixe em branco se não souber)</t>
+          <t>Código INEP (apenas se for local; 8 dígitos)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Q10.1. Este diagnóstico, no conjunto, reflete a realidade da escola e do território?</t>
+          <t>Q10.1. Este diagnóstico, no conjunto, reflete a realidade do local e do território?</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Q10.6. Que transformação a escola espera alcançar com os planos construídos?</t>
+          <t>Q10.6. Que transformação o local espera alcançar com os planos construídos?</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Q10.7. Nossa escola será mais resiliente quando...</t>
+          <t>Q10.7. Nosso local será mais resiliente quando...</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">

--- a/kobo/gestores_semana5_diagnostico.xlsx
+++ b/kobo/gestores_semana5_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>identificacao</t>
+          <t>tcle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Identificação (igual à Semana 1)</t>
+          <t>Termo de Consentimento</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -598,25 +598,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>id_escola</t>
+          <t>tcle_texto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nome do local de atuação</t>
+          <t>TERMO DE CONSENTIMENTO LIVRE E ESCLARECIDO. Você está sendo convidado(a) a responder este Diagnóstico Socioambiental, Climático e de Educação Ambiental. A participação é voluntária: você pode recusar ou interromper a qualquer momento, sem qualquer prejuízo. As informações fornecidas, inclusive seus dados pessoais e de identificação (nome, função, local de atuação), serão tratadas com sigilo, NÃO serão compartilhadas com terceiros de forma que identifique você ou o seu local de atuação e serão utilizadas apenas para compor um banco de dados do projeto. Eventuais resultados e relatórios serão apresentados somente de forma agregada, sem identificar pessoas. O tratamento dos dados segue a Lei Geral de Proteção de Dados (Lei nº 13.709/2018). Em caso de dúvidas, procure a equipe responsável pelo projeto.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -626,58 +622,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one concordo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>id_inep</t>
+          <t>tcle_consentimento</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Código INEP (apenas se for local; 8 dígitos)</t>
+          <t>Li o termo acima e concordo em participar e em ter minhas respostas e meus dados utilizados no banco de dados do projeto, nos termos descritos.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>regex(., '^[0-9]{8}$')</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>O código INEP deve ter 8 dígitos.</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>id_nome</t>
+          <t>tcle_recusa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seu nome</t>
+          <t>Sem o seu consentimento não é possível continuar. Obrigado(a) pelo seu tempo! Você pode encerrar o formulário.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>${tcle_consentimento} = 'nao_concordo'</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -707,17 +699,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>etapa8</t>
+          <t>conteudo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Etapa 8 — Educomunicação</t>
+          <t>Diagnóstico</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>${tcle_consentimento} = 'concordo'</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comunic</t>
+          <t>identificacao</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano de educomunicação (um por ação — use "Adicionar" para cada ação)</t>
+          <t>Identificação (igual à Semana 1)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -755,12 +751,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>com_acao</t>
+          <t>id_escola</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ação: título do problema confirmado</t>
+          <t>Nome do local de atuação</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,25 +774,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple com_final</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>com_purpose</t>
+          <t>id_inep</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finalidades (COM_PURPOSE)</t>
+          <t>Código INEP (apenas se for local; 8 dígitos)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9]{8}$')</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O código INEP deve ter 8 dígitos.</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -807,21 +811,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>com_purpose_outro</t>
+          <t>id_nome</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Seu nome</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>selected(${com_purpose}, 'outro')</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -830,19 +834,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple com_publico</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>com_audience</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Públicos (COM_AUDIENCE)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -854,26 +850,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>com_audience_outro</t>
+          <t>etapa8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Etapa 8 — Educomunicação</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>selected(${com_audience}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -882,27 +874,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>com_central_message</t>
+          <t>comunic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mensagem central (COM_CENTRAL_MESSAGE)</t>
+          <t>Plano de educomunicação (um por ação — use "Adicionar" para cada ação)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -910,21 +898,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple com_escuta</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>com_listening_channels</t>
+          <t>com_acao</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Canais de escuta (COM_LISTENING_CHANNELS)</t>
+          <t>Ação: título do problema confirmado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -934,26 +926,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple com_final</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>com_listening_channels_outro</t>
+          <t>com_purpose</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Finalidades (COM_PURPOSE)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>selected(${com_listening_channels}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -962,22 +950,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple com_midia</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>com_media</t>
+          <t>com_purpose_outro</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mídias/formatos (COM_MEDIA)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>selected(${com_purpose}, 'outro')</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -986,26 +978,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple com_publico</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>com_media_outro</t>
+          <t>com_audience</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Públicos (COM_AUDIENCE)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>selected(${com_media}, 'outro')</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1014,22 +1002,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple com_barr</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>com_access_barriers</t>
+          <t>com_audience_outro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Barreiras de acesso (COM_ACCESS_BARRIERS)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>selected(${com_audience}, 'outro')</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1043,22 +1035,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>com_access_barriers_outro</t>
+          <t>com_central_message</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Especifique (Outro)</t>
+          <t>Mensagem central (COM_CENTRAL_MESSAGE)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>selected(${com_access_barriers}, 'outro')</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -1066,27 +1058,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple com_escuta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>com_access_needs</t>
+          <t>com_listening_channels</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Necessidades de acessibilidade (COM_ACCESS_NEEDS)</t>
+          <t>Canais de escuta (COM_LISTENING_CHANNELS)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -1099,22 +1087,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>com_access_strategies</t>
+          <t>com_listening_channels_outro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estratégias de acessibilidade (COM_ACCESS_STRATEGIES)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>selected(${com_listening_channels}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -1122,17 +1110,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_multiple com_produz</t>
+          <t>select_multiple com_midia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>com_producers</t>
+          <t>com_media</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Quem produz (COM_PRODUCERS)</t>
+          <t>Mídias/formatos (COM_MEDIA)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1151,7 +1139,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>com_producers_outro</t>
+          <t>com_media_outro</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1163,7 +1151,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>selected(${com_producers}, 'outro')</t>
+          <t>selected(${com_media}, 'outro')</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1174,17 +1162,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_one com_decisao</t>
+          <t>select_multiple com_barr</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>com_student_decision</t>
+          <t>com_access_barriers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nível de decisão dos estudantes (COM_STUDENT_DECISION)</t>
+          <t>Barreiras de acesso (COM_ACCESS_BARRIERS)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1203,22 +1191,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>com_timing</t>
+          <t>com_access_barriers_outro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Momento em relação à ação (COM_TIMING)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>selected(${com_access_barriers}, 'outro')</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -1226,15 +1214,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>com_access_needs</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Necessidades de acessibilidade (COM_ACCESS_NEEDS)</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -1242,15 +1242,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>com_access_strategies</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Estratégias de acessibilidade (COM_ACCESS_STRATEGIES)</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -1258,17 +1270,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_multiple com_produz</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>etapa9</t>
+          <t>com_producers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Etapa 9 — Monitoramento</t>
+          <t>Quem produz (COM_PRODUCERS)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1282,22 +1294,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>monit</t>
+          <t>com_producers_outro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indicador de monitoramento (um por indicador — use "Adicionar" para cada um)</t>
+          <t>Especifique (Outro)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>selected(${com_producers}, 'outro')</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1306,25 +1322,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one com_decisao</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>mon_acao</t>
+          <t>com_student_decision</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ação: título do problema confirmado</t>
+          <t>Nível de decisão dos estudantes (COM_STUDENT_DECISION)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1339,18 +1351,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mon_indicator_name</t>
+          <t>com_timing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nome do indicador (MON_INDICATOR_NAME)</t>
+          <t>Momento em relação à ação (COM_TIMING)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -1358,19 +1374,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_one ind_tipo</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>mon_indicator_type</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tipo (MON_INDICATOR_TYPE)</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -1382,27 +1390,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>mon_measurement</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Como será medido (MON_MEASUREMENT)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -1410,17 +1406,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>select_one sim_nao</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mon_sabe_baseline</t>
+          <t>etapa9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sabemos a linha de base atual?</t>
+          <t>Etapa 9 — Monitoramento</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1434,26 +1430,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>mon_baseline</t>
+          <t>monit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Linha de base (MON_BASELINE)</t>
+          <t>Indicador de monitoramento (um por indicador — use "Adicionar" para cada um)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>${mon_sabe_baseline}='sim'</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1467,16 +1459,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>mon_target</t>
+          <t>mon_acao</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Meta (MON_TARGET)</t>
+          <t>Ação: título do problema confirmado</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1491,12 +1487,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>mon_source</t>
+          <t>mon_indicator_name</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fonte de verificação (MON_SOURCE)</t>
+          <t>Nome do indicador (MON_INDICATOR_NAME)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1510,17 +1506,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>select_one periodicidade</t>
+          <t>select_one ind_tipo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>mon_periodicity</t>
+          <t>mon_indicator_type</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Periodicidade (MON_PERIODICITY)</t>
+          <t>Tipo (MON_INDICATOR_TYPE)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1539,18 +1535,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>mon_responsible</t>
+          <t>mon_measurement</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Responsável (MON_RESPONSIBLE)</t>
+          <t>Como será medido (MON_MEASUREMENT)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -1558,27 +1558,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mon_qual_change</t>
+          <t>mon_sabe_baseline</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mudança qualitativa observada até agora (MON_QUALITATIVE_CHANGE)</t>
+          <t>Sabemos a linha de base atual?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -1591,22 +1587,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>mon_qual_recognition</t>
+          <t>mon_baseline</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Como reconheceremos essa mudança? (MON_QUALITATIVE_RECOGNITION)</t>
+          <t>Linha de base (MON_BASELINE)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>${mon_sabe_baseline}='sim'</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -1614,11 +1610,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>end_repeat</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>mon_target</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Meta (MON_TARGET)</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -1630,11 +1634,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>mon_source</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fonte de verificação (MON_SOURCE)</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -1646,17 +1658,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one periodicidade</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>etapa10</t>
+          <t>mon_periodicity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Etapa 10 — Síntese</t>
+          <t>Periodicidade (MON_PERIODICITY)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1670,17 +1682,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>e10_nota</t>
+          <t>mon_responsible</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Esta etapa não substitui a leitura já construída — ela organiza uma síntese final a partir do que foi registrado.</t>
+          <t>Responsável (MON_RESPONSIBLE)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1694,27 +1706,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>select_one sim_nao_ns</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>q10_1</t>
+          <t>mon_qual_change</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Q10.1. Este diagnóstico, no conjunto, reflete a realidade do local e do território?</t>
+          <t>Mudança qualitativa observada até agora (MON_QUALITATIVE_CHANGE)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -1727,12 +1739,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>q10_2</t>
+          <t>mon_qual_recognition</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Q10.2. Há algo que precisa ser revisado antes de considerar este diagnóstico concluído?</t>
+          <t>Como reconheceremos essa mudança? (MON_QUALITATIVE_RECOGNITION)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1750,27 +1762,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>q10_3</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Q10.3. Qual o principal desafio revelado por este diagnóstico?</t>
-        </is>
-      </c>
+          <t>end_repeat</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -1778,27 +1778,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>q10_4</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Q10.4. Qual a principal capacidade/potencialidade revelada?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -1806,27 +1794,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>q10_5</t>
+          <t>etapa10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Q10.5. Qual parceria é mais prioritária para os próximos passos?</t>
+          <t>Etapa 10 — Síntese</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -1834,27 +1818,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>q10_6</t>
+          <t>e10_nota</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Q10.6. Que transformação o local espera alcançar com os planos construídos?</t>
+          <t>Esta etapa não substitui a leitura já construída — ela organiza uma síntese final a partir do que foi registrado.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -1862,35 +1842,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one sim_nao_ns</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>q10_7</t>
+          <t>q10_1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Q10.7. Nosso local será mais resiliente quando...</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Complete a frase com suas próprias palavras — ela encerra este diagnóstico.</t>
-        </is>
-      </c>
+          <t>Q10.1. Este diagnóstico, no conjunto, reflete a realidade do local e do território?</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -1898,18 +1870,210 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>q10_2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Q10.2. Há algo que precisa ser revisado antes de considerar este diagnóstico concluído?</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>q10_3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Q10.3. Qual o principal desafio revelado por este diagnóstico?</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>q10_4</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Q10.4. Qual a principal capacidade/potencialidade revelada?</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>q10_5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Q10.5. Qual parceria é mais prioritária para os próximos passos?</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>q10_6</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Q10.6. Que transformação o local espera alcançar com os planos construídos?</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>q10_7</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Q10.7. Nosso local será mais resiliente quando...</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Complete a frase com suas próprias palavras — ela encerra este diagnóstico.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1922,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1945,34 +2109,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sim_nao_ns</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Sim, concordo em participar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sim_nao_ns</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>nao_concordo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não concordo</t>
         </is>
       </c>
     </row>
@@ -1984,80 +2148,80 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nao_sabemos</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Não sabemos</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sim_nao</t>
+          <t>sim_nao_ns</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sim_nao</t>
+          <t>sim_nao_ns</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>nao_sabemos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Não sabemos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>sim_nao</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>informar</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Informar</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>sim_nao</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sensibilizar</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sensibilizar</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2233,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mobilizar</t>
+          <t>informar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mobilizar</t>
+          <t>Informar</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2250,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>prestar_contas</t>
+          <t>sensibilizar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prestar contas</t>
+          <t>Sensibilizar</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2267,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dar_voz_a_comunidade</t>
+          <t>mobilizar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dar voz à comunidade</t>
+          <t>Mobilizar</t>
         </is>
       </c>
     </row>
@@ -2120,46 +2284,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>prestar_contas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Prestar contas</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>dar_voz_a_comunidade</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Dar voz à comunidade</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2335,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2352,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2369,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -2222,46 +2386,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>caixa_de_sugestoes</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Caixa de sugestões</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>roda_de_conversa</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Roda de conversa</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2437,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>formulario</t>
+          <t>caixa_de_sugestoes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Formulário</t>
+          <t>Caixa de sugestões</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2454,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>roda_de_conversa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Roda de conversa</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2471,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>reuniao</t>
+          <t>formulario</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Reunião</t>
+          <t>Formulário</t>
         </is>
       </c>
     </row>
@@ -2324,46 +2488,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cartaz</t>
+          <t>reuniao</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cartaz</t>
+          <t>Reunião</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>radio_escolar</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rádio escolar</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2375,12 +2539,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>cartaz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Cartaz</t>
         </is>
       </c>
     </row>
@@ -2392,12 +2556,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>radio_escolar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Rádio escolar</t>
         </is>
       </c>
     </row>
@@ -2409,12 +2573,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jornal_mural</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jornal mural</t>
+          <t>Vídeo</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2590,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>teatro</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Teatro</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2607,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>podcast</t>
+          <t>jornal_mural</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Podcast</t>
+          <t>Jornal mural</t>
         </is>
       </c>
     </row>
@@ -2460,46 +2624,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>teatro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Teatro</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>idioma_linguagem_tecnica</t>
+          <t>podcast</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Idioma/linguagem técnica</t>
+          <t>Podcast</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>acessibilidade_para_pessoas_com_</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Acessibilidade para pessoas com deficiência</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2511,12 +2675,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>falta_de_conectividade</t>
+          <t>idioma_linguagem_tecnica</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Falta de conectividade</t>
+          <t>Idioma/linguagem técnica</t>
         </is>
       </c>
     </row>
@@ -2528,12 +2692,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>alfabetizacao</t>
+          <t>acessibilidade_para_pessoas_com_</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alfabetização</t>
+          <t>Acessibilidade para pessoas com deficiência</t>
         </is>
       </c>
     </row>
@@ -2545,46 +2709,46 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>falta_de_conectividade</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Falta de conectividade</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>com_produz</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>alfabetizacao</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Alfabetização</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>com_produz</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2760,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>comunicacao_escolar</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Comunicação escolar</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -2613,12 +2777,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>parceiros_externos</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Parceiros externos</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -2630,46 +2794,46 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>comunicacao_escolar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Comunicação escolar</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_produz</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>parceiros_externos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Parceiros externos</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_produz</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sao_consultados</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>São consultados</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2845,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>colaboram_na_producao</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Colaboram na produção</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
@@ -2698,46 +2862,46 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>decidem_conteudo_formato</t>
+          <t>sao_consultados</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Decidem conteúdo/formato</t>
+          <t>São consultados</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>processo</t>
+          <t>colaboram_na_producao</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Processo</t>
+          <t>Colaboram na produção</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>participacao</t>
+          <t>decidem_conteudo_formato</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Participação</t>
+          <t>Decidem conteúdo/formato</t>
         </is>
       </c>
     </row>
@@ -2749,46 +2913,46 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>processo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Processo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>participacao</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Participação</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>bimestral</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bimestral</t>
+          <t>Resultado</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2964,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>trimestral</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2981,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>semestral</t>
+          <t>bimestral</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Semestral</t>
+          <t>Bimestral</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2998,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>trimestral</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Trimestral</t>
         </is>
       </c>
     </row>
@@ -2851,10 +3015,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>semestral</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>periodicidade</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>periodicidade</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>por_evento</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Por evento</t>
         </is>
@@ -2924,7 +3122,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>pages</t>
+          <t>theme-grid no-text-transform</t>
         </is>
       </c>
     </row>

--- a/kobo/gestores_semana5_diagnostico.xlsx
+++ b/kobo/gestores_semana5_diagnostico.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2062,11 +2062,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>confirmacao</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Confirmação final</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
@@ -2074,6 +2082,90 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>confirmacao_msg</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Semana 5/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>select_one confirmo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>confirmacao_envio</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Revisei minhas respostas e confirmo o envio.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2086,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2109,17 +2201,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>concordo</t>
+          <t>confirmo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>concordo</t>
+          <t>confirmo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sim, concordo em participar</t>
+          <t>Sim, confirmo o envio</t>
         </is>
       </c>
     </row>
@@ -2131,29 +2223,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nao_concordo</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Não concordo</t>
+          <t>Sim, concordo em participar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sim_nao_ns</t>
+          <t>concordo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao_concordo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não concordo</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2257,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -2182,29 +2274,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nao_sabemos</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Não sabemos</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sim_nao</t>
+          <t>sim_nao_ns</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao_sabemos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não sabemos</t>
         </is>
       </c>
     </row>
@@ -2216,29 +2308,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>sim_nao</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>informar</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Informar</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2342,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sensibilizar</t>
+          <t>informar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sensibilizar</t>
+          <t>Informar</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2359,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mobilizar</t>
+          <t>sensibilizar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mobilizar</t>
+          <t>Sensibilizar</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2376,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>prestar_contas</t>
+          <t>mobilizar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prestar contas</t>
+          <t>Mobilizar</t>
         </is>
       </c>
     </row>
@@ -2301,12 +2393,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dar_voz_a_comunidade</t>
+          <t>prestar_contas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dar voz à comunidade</t>
+          <t>Prestar contas</t>
         </is>
       </c>
     </row>
@@ -2318,29 +2410,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>dar_voz_a_comunidade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Dar voz à comunidade</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2444,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2461,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2478,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
@@ -2403,12 +2495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
@@ -2420,29 +2512,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>caixa_de_sugestoes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Caixa de sugestões</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2546,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roda_de_conversa</t>
+          <t>caixa_de_sugestoes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Roda de conversa</t>
+          <t>Caixa de sugestões</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2563,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>formulario</t>
+          <t>roda_de_conversa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Formulário</t>
+          <t>Roda de conversa</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2580,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>formulario</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Formulário</t>
         </is>
       </c>
     </row>
@@ -2505,12 +2597,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>reuniao</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reunião</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -2522,29 +2614,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>reuniao</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Reunião</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cartaz</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cartaz</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2648,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>radio_escolar</t>
+          <t>cartaz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rádio escolar</t>
+          <t>Cartaz</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2665,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>radio_escolar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Rádio escolar</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2682,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Vídeo</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2699,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jornal_mural</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jornal mural</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2716,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>teatro</t>
+          <t>jornal_mural</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Teatro</t>
+          <t>Jornal mural</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2733,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>podcast</t>
+          <t>teatro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Podcast</t>
+          <t>Teatro</t>
         </is>
       </c>
     </row>
@@ -2658,29 +2750,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>podcast</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Podcast</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>idioma_linguagem_tecnica</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Idioma/linguagem técnica</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2692,12 +2784,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>acessibilidade_para_pessoas_com_</t>
+          <t>idioma_linguagem_tecnica</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Acessibilidade para pessoas com deficiência</t>
+          <t>Idioma/linguagem técnica</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2801,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>falta_de_conectividade</t>
+          <t>acessibilidade_para_pessoas_com_</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Falta de conectividade</t>
+          <t>Acessibilidade para pessoas com deficiência</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2818,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>alfabetizacao</t>
+          <t>falta_de_conectividade</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alfabetização</t>
+          <t>Falta de conectividade</t>
         </is>
       </c>
     </row>
@@ -2743,29 +2835,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>alfabetizacao</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Alfabetização</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>com_produz</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2869,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2886,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>comunicacao_escolar</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Comunicação escolar</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2903,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>parceiros_externos</t>
+          <t>comunicacao_escolar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Parceiros externos</t>
+          <t>Comunicação escolar</t>
         </is>
       </c>
     </row>
@@ -2828,29 +2920,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>parceiros_externos</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Parceiros externos</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_produz</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2954,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>sao_consultados</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>São consultados</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2971,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>colaboram_na_producao</t>
+          <t>sao_consultados</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Colaboram na produção</t>
+          <t>São consultados</t>
         </is>
       </c>
     </row>
@@ -2896,29 +2988,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>decidem_conteudo_formato</t>
+          <t>colaboram_na_producao</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Decidem conteúdo/formato</t>
+          <t>Colaboram na produção</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>processo</t>
+          <t>decidem_conteudo_formato</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Processo</t>
+          <t>Decidem conteúdo/formato</t>
         </is>
       </c>
     </row>
@@ -2930,12 +3022,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>participacao</t>
+          <t>processo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Participação</t>
+          <t>Processo</t>
         </is>
       </c>
     </row>
@@ -2947,29 +3039,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>participacao</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Participação</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Resultado</t>
         </is>
       </c>
     </row>
@@ -2981,12 +3073,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bimestral</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bimestral</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -2998,12 +3090,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>trimestral</t>
+          <t>bimestral</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Bimestral</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3107,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>semestral</t>
+          <t>trimestral</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Semestral</t>
+          <t>Trimestral</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3124,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>semestral</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Semestral</t>
         </is>
       </c>
     </row>
@@ -3049,10 +3141,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>periodicidade</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>por_evento</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Por evento</t>
         </is>

--- a/kobo/gestores_semana5_diagnostico.xlsx
+++ b/kobo/gestores_semana5_diagnostico.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Semana 5/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir.</t>
+          <t>Semana 5/5 concluída. Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
